--- a/artfynd/A 28732-2022 artfynd.xlsx
+++ b/artfynd/A 28732-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121707209</v>
       </c>
       <c r="B2" t="n">
-        <v>98019</v>
+        <v>98037</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 28732-2022 artfynd.xlsx
+++ b/artfynd/A 28732-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121707209</v>
       </c>
       <c r="B2" t="n">
-        <v>98037</v>
+        <v>98039</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 28732-2022 artfynd.xlsx
+++ b/artfynd/A 28732-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121707209</v>
       </c>
       <c r="B2" t="n">
-        <v>98039</v>
+        <v>98046</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 28732-2022 artfynd.xlsx
+++ b/artfynd/A 28732-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121707209</v>
       </c>
       <c r="B2" t="n">
-        <v>98046</v>
+        <v>98055</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
